--- a/naver-place-crawler/results_nail/제주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/제주_네일샵.xlsx
@@ -421,12 +421,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1475</v>
+        <v>1480</v>
       </c>
       <c r="Q2" t="n">
         <v>339</v>
       </c>
       <c r="R2" t="n">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>리게인 앤네일유리</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>jujuhehe6466@naver.com</t>
-        </is>
-      </c>
+          <t>비비엔네일</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1485-8448</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 원노형남1길 37 1층</t>
+          <t>제주 제주시 국기로 34 5층 필솝 내 위치</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/regain_nailuri?igsh=Zzc2aWI1eTV6cnZ6&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_HhFIxj/chat</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,12 +701,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wyhoroi</t>
+          <t>https://talk.naver.com/ct/w4sb11</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>157</v>
+        <v>666</v>
       </c>
       <c r="Q3" t="n">
-        <v>345</v>
+        <v>24</v>
       </c>
       <c r="R3" t="n">
-        <v>502</v>
+        <v>690</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1321996330</t>
+          <t>1710109440</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1321996330</t>
+          <t>https://m.place.naver.com/place/1710109440</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -824,10 +816,10 @@
         <v>761</v>
       </c>
       <c r="Q4" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="R4" t="n">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -858,25 +850,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>브리에네일</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>chdn810@naver.com</t>
-        </is>
-      </c>
+          <t>리게인 앤네일유리</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1485-8448</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍중앙로 55 1층</t>
+          <t>제주 제주시 원노형남1길 37 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brillernail1112</t>
+          <t>https://www.instagram.com/regain_nailuri?igsh=Zzc2aWI1eTV6cnZ6&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -896,10 +888,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyhoroi</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -911,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>334</v>
+        <v>170</v>
       </c>
       <c r="Q5" t="n">
-        <v>118</v>
+        <v>484</v>
       </c>
       <c r="R5" t="n">
-        <v>452</v>
+        <v>654</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1481282228</t>
+          <t>1321996330</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1481282228</t>
+          <t>https://m.place.naver.com/place/1321996330</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -948,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일바다 닥터풋클린 본점</t>
+          <t>리본뷰티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tjsgmlzoq92@naver.com</t>
+          <t>rebornbeauty_jeju@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1396-4182</t>
+          <t>0507-1332-0795</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 서귀포시 대청로25번길 6-9 상가동 1층 102호 네일바다닥터풋클린</t>
+          <t>제주 제주시 청사로 67</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_bada_amanda</t>
+          <t>https://blog.naver.com/rebornbeauty_jeju</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -985,18 +981,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5yziu</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1005,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>472</v>
+        <v>559</v>
       </c>
       <c r="Q6" t="n">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="R6" t="n">
-        <v>595</v>
+        <v>660</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1056365302</t>
+          <t>1523223228</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056365302</t>
+          <t>https://m.place.naver.com/place/1523223228</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1042,34 +1042,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인더블룸</t>
+          <t>벨르네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>boseong37@naver.com</t>
+          <t>rlatpdml@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1333-8096</t>
+          <t>0507-1419-0485</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 제주시 신대로15길 13 1층</t>
+          <t>제주 서귀포시 홍중로 119-2 602동 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inthebloom_jejunail</t>
+          <t>http://pf.kakao.com/_AxnyeG</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4orp4</t>
+          <t>https://talk.naver.com/ct/w5zplw</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="Q7" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>493</v>
+        <v>432</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1369211176</t>
+          <t>1420634838</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1369211176</t>
+          <t>https://m.place.naver.com/place/1420634838</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1140,34 +1140,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>벨르네일</t>
+          <t>애프터네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>c0___0x@naver.com</t>
+          <t>j-bonny@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1419-0485</t>
+          <t>0507-1360-8833</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 서귀포시 홍중로 119-2 602동 1층</t>
+          <t>제주 제주시 인다4길 31 1층 애프터네일</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_AxnyeG</t>
+          <t>https://www.instagram.com/after.nail_jeju</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zplw</t>
+          <t>https://talk.naver.com/ct/wack2oc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1201,13 +1201,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>429</v>
+        <v>298</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="R8" t="n">
-        <v>429</v>
+        <v>372</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,17 +1216,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1420634838</t>
+          <t>1429578252</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420634838</t>
+          <t>https://m.place.naver.com/place/1429578252</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1238,29 +1238,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>이손네일 제주</t>
+          <t>네일드초이</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dlths2647@naver.com</t>
+          <t>tkatns289@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1338-2647</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 제주시 노형8길 19 3층</t>
+          <t>제주 서귀포시 서호남로32번길 10-2 1층 건앤로빈스 안</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dlths2647</t>
+          <t>https://www.instagram.com/nail_de_choi?igsh=MXVlMTZkdm5henc2Zw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1275,7 +1271,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1285,7 +1281,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4o3ky</t>
+          <t>https://talk.naver.com/ct/w92mh5i</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1299,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>72</v>
+        <v>219</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>92</v>
+        <v>220</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1314,17 +1310,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1675626387</t>
+          <t>1823333907</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1675626387</t>
+          <t>https://m.place.naver.com/place/1823333907</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1437,11 +1433,7 @@
           <t>프롬미네일</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>foresora@naver.com</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -1516,7 +1508,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/제주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/제주_네일샵.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="Q2" t="n">
         <v>339</v>
       </c>
       <c r="R2" t="n">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,26 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>비비엔네일</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>리게인 앤네일유리</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>crcr_15@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1485-8448</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>제주 제주시 국기로 34 5층 필솝 내 위치</t>
+          <t>제주 제주시 원노형남1길 37 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_HhFIxj/chat</t>
+          <t>https://www.instagram.com/regain_nailuri?igsh=Zzc2aWI1eTV6cnZ6&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -701,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sb11</t>
+          <t>https://talk.naver.com/ct/wyhoroi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>666</v>
+        <v>176</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>541</v>
       </c>
       <c r="R3" t="n">
-        <v>690</v>
+        <v>717</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1710109440</t>
+          <t>1321996330</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1710109440</t>
+          <t>https://m.place.naver.com/place/1321996330</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>메이크유</t>
+          <t>리본뷰티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>gpals6442@naver.com</t>
+          <t>rebornbeauty_jeju@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1349-2465</t>
+          <t>0507-1332-0795</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>제주 제주시 연오로 110 1층</t>
+          <t>제주 제주시 청사로 67</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/m.a.k.e_u/</t>
+          <t>https://blog.naver.com/rebornbeauty_jeju</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,7 +797,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -799,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4uclk</t>
+          <t>https://talk.naver.com/ct/w5yziu</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>761</v>
+        <v>559</v>
       </c>
       <c r="Q4" t="n">
-        <v>181</v>
+        <v>101</v>
       </c>
       <c r="R4" t="n">
-        <v>942</v>
+        <v>660</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1320850750</t>
+          <t>1523223228</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1320850750</t>
+          <t>https://m.place.naver.com/place/1523223228</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -850,25 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>리게인 앤네일유리</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>메이크유</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gpals6442@naver.com</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1485-8448</t>
+          <t>0507-1349-2465</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>제주 제주시 원노형남1길 37 1층</t>
+          <t>제주 제주시 연오로 110 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/regain_nailuri?igsh=Zzc2aWI1eTV6cnZ6&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/m.a.k.e_u/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -893,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wyhoroi</t>
+          <t>https://talk.naver.com/ct/w4uclk</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>170</v>
+        <v>762</v>
       </c>
       <c r="Q5" t="n">
-        <v>484</v>
+        <v>179</v>
       </c>
       <c r="R5" t="n">
-        <v>654</v>
+        <v>941</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1321996330</t>
+          <t>1320850750</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1321996330</t>
+          <t>https://m.place.naver.com/place/1320850750</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,34 +956,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>리본뷰티</t>
+          <t>비비엔네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rebornbeauty_jeju@naver.com</t>
+          <t>kjy941123@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1332-0795</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>제주 제주시 청사로 67</t>
+          <t>제주 제주시 국기로 34 5층 필솝 내 위치</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rebornbeauty_jeju</t>
+          <t>http://pf.kakao.com/_HhFIxj/chat</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -981,7 +989,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -991,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5yziu</t>
+          <t>https://talk.naver.com/ct/w4sb11</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1005,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>559</v>
+        <v>665</v>
       </c>
       <c r="Q6" t="n">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>660</v>
+        <v>689</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1523223228</t>
+          <t>1710109440</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1523223228</t>
+          <t>https://m.place.naver.com/place/1710109440</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1042,34 +1050,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>벨르네일</t>
+          <t>인더블룸</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rlatpdml@naver.com</t>
+          <t>boseong37@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1419-0485</t>
+          <t>0507-1333-8096</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>제주 서귀포시 홍중로 119-2 602동 1층</t>
+          <t>제주 제주시 신대로15길 13 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_AxnyeG</t>
+          <t>https://www.instagram.com/inthebloom_jejunail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1089,12 +1097,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zplw</t>
+          <t>https://talk.naver.com/ct/w4orp4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1103,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>432</v>
+        <v>372</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="R7" t="n">
-        <v>432</v>
+        <v>493</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1118,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1420634838</t>
+          <t>1369211176</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1420634838</t>
+          <t>https://m.place.naver.com/place/1369211176</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1140,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>애프터네일</t>
+          <t>벨르네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>j-bonny@naver.com</t>
+          <t>rlatpdml@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1360-8833</t>
+          <t>0507-1419-0485</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>제주 제주시 인다4길 31 1층 애프터네일</t>
+          <t>제주 서귀포시 홍중로 119-2 602동 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/after.nail_jeju</t>
+          <t>http://pf.kakao.com/_AxnyeG</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1187,12 +1195,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wack2oc</t>
+          <t>https://talk.naver.com/ct/w5zplw</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1201,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>298</v>
+        <v>432</v>
       </c>
       <c r="Q8" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1216,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1429578252</t>
+          <t>1420634838</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429578252</t>
+          <t>https://m.place.naver.com/place/1420634838</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1238,25 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>네일드초이</t>
+          <t>린네일 제주노형점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tkatns289@naver.com</t>
+          <t>tjsgmlzoq92@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1397-8687</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>제주 서귀포시 서호남로32번길 10-2 1층 건앤로빈스 안</t>
+          <t>제주 제주시 진군2길 15-9 1층 린네일</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_choi?igsh=MXVlMTZkdm5henc2Zw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1266,7 +1278,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1281,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w92mh5i</t>
+          <t>https://talk.naver.com/ct/w5zfje</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1291,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>219</v>
+        <v>500</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1823333907</t>
+          <t>1272276511</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1823333907</t>
+          <t>https://m.place.naver.com/place/1272276511</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1332,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>미네일</t>
+          <t>애프터네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>onelovekmh@naver.com</t>
+          <t>j-bonny@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>064-732-4199</t>
+          <t>0507-1360-8833</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 서귀포시 동홍남로 73 1층 미네일</t>
+          <t>제주 제주시 인다4길 31 1층 애프터네일</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/minail7324199</t>
+          <t>https://www.instagram.com/after.nail_jeju</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1379,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w41yms</t>
+          <t>https://talk.naver.com/ct/wack2oc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1393,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>31</v>
+        <v>298</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="R10" t="n">
-        <v>32</v>
+        <v>372</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37852718</t>
+          <t>1429578252</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37852718</t>
+          <t>https://m.place.naver.com/place/1429578252</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1430,21 +1442,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>프롬미네일</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>네일드초이</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>tkatns289@naver.com</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 제주시 인다4길 15-2 인다포레 1층 프롬미네일</t>
+          <t>제주 서귀포시 서호남로32번길 10-2 1층 건앤로빈스 안</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/from.me_nail</t>
+          <t>https://www.instagram.com/nail_de_choi?igsh=MXVlMTZkdm5henc2Zw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1469,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5x08p</t>
+          <t>https://talk.naver.com/ct/w92mh5i</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1483,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>64</v>
+        <v>219</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>67</v>
+        <v>220</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,17 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1913557462</t>
+          <t>1823333907</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1913557462</t>
+          <t>https://m.place.naver.com/place/1823333907</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/제주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/제주_네일샵.xlsx
@@ -726,10 +726,10 @@
         <v>176</v>
       </c>
       <c r="Q3" t="n">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="R3" t="n">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -959,11 +959,7 @@
           <t>비비엔네일</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>kjy941123@naver.com</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -1344,29 +1340,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>애프터네일</t>
+          <t>네일드초이</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>j-bonny@naver.com</t>
+          <t>tkatns289@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1360-8833</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>제주 제주시 인다4길 31 1층 애프터네일</t>
+          <t>제주 서귀포시 서호남로32번길 10-2 1층 건앤로빈스 안</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/after.nail_jeju</t>
+          <t>https://www.instagram.com/nail_de_choi?igsh=MXVlMTZkdm5henc2Zw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1383,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wack2oc</t>
+          <t>https://talk.naver.com/ct/w92mh5i</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1397,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>298</v>
+        <v>219</v>
       </c>
       <c r="Q10" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>372</v>
+        <v>220</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1412,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1429578252</t>
+          <t>1823333907</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429578252</t>
+          <t>https://m.place.naver.com/place/1823333907</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1442,25 +1434,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일드초이</t>
+          <t>버니네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tkatns289@naver.com</t>
+          <t>shh878185@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1370-8185</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>제주 서귀포시 서호남로32번길 10-2 1층 건앤로빈스 안</t>
+          <t>제주 제주시 연동8길 4 버니네일</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_de_choi?igsh=MXVlMTZkdm5henc2Zw%3D%3D&amp;utm_source=qr</t>
+          <t>http://instagram.com/bunnynail_jeju</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,7 +1481,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w92mh5i</t>
+          <t>https://talk.naver.com/ct/w4265e</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1495,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="R11" t="n">
-        <v>220</v>
+        <v>109</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1510,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1823333907</t>
+          <t>1229054447</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1823333907</t>
+          <t>https://m.place.naver.com/place/1229054447</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_nail/제주_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/제주_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V329"/>
+  <dimension ref="A1:V418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30367,30 +30367,34 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>달콤살롱</t>
+          <t>버니네일</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>830mijung@naver.com</t>
+          <t>shh878185@naver.com</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0507-1370-8185</t>
+        </is>
+      </c>
       <c r="F326" t="inlineStr"/>
       <c r="G326" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 정존9길 19 1층 달콤살롱</t>
+          <t>제주특별자치도 제주시 연동8길 4 버니네일</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mippeum.nail?igsh=MXFsc21nb2x2Y3g0dA==</t>
+          <t>http://instagram.com/bunnynail_jeju</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -30425,13 +30429,13 @@
         </is>
       </c>
       <c r="P326" t="n">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="Q326" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="R326" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="S326" t="inlineStr">
         <is>
@@ -30440,12 +30444,12 @@
       </c>
       <c r="T326" t="inlineStr">
         <is>
-          <t>1728912841</t>
+          <t>1229054447</t>
         </is>
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1728912841</t>
+          <t>https://m.place.naver.com/place/1229054447</t>
         </is>
       </c>
       <c r="V326" t="inlineStr">
@@ -30457,34 +30461,30 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>속눈썹증모,연장</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>엘리제토탈뷰티</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>giobeauty@naver.com</t>
-        </is>
-      </c>
+          <t>베베뷰티</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>064-792-6456</t>
+          <t>0507-1424-2575</t>
         </is>
       </c>
       <c r="F327" t="inlineStr"/>
       <c r="G327" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 대정읍 하모중앙로 63-1</t>
+          <t>제주특별자치도 제주시 관덕로15길 2 2층</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_bebe_beauty.nail/profilecard/?igsh=MXYzN3A5ZHMzOTl2Yg==</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -30494,7 +30494,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -30515,17 +30515,17 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P327" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="Q327" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R327" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="S327" t="inlineStr">
         <is>
@@ -30534,12 +30534,12 @@
       </c>
       <c r="T327" t="inlineStr">
         <is>
-          <t>1541813488</t>
+          <t>1950191890</t>
         </is>
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1541813488</t>
+          <t>https://m.place.naver.com/place/1950191890</t>
         </is>
       </c>
       <c r="V327" t="inlineStr">
@@ -30551,39 +30551,35 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>디자인 수지</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>design-suji@naver.com</t>
-        </is>
-      </c>
+          <t>인생네일</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>0507-1309-2058</t>
+          <t>0507-1336-3319</t>
         </is>
       </c>
       <c r="F328" t="inlineStr"/>
       <c r="G328" t="inlineStr">
         <is>
-          <t>제주특별자치도 제주시 노형로 21 2층</t>
+          <t>제주특별자치도 서귀포시 신서로32번길 10 베스킨라빈스 옆</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/design-suji</t>
+          <t>http://www.instagram.com/artist_lavie</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -30609,17 +30605,17 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P328" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q328" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R328" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
@@ -30628,12 +30624,12 @@
       </c>
       <c r="T328" t="inlineStr">
         <is>
-          <t>1189515208</t>
+          <t>1712515646</t>
         </is>
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189515208</t>
+          <t>https://m.place.naver.com/place/1712515646</t>
         </is>
       </c>
       <c r="V328" t="inlineStr">
@@ -30645,34 +30641,30 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>카페,디저트</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>엘에프</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>woojoo90@naver.com</t>
-        </is>
-      </c>
+          <t>미네일</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>0507-1497-0767</t>
+          <t>064-732-4199</t>
         </is>
       </c>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시 이어도로 301 4호 엘에프 LF</t>
+          <t>제주특별자치도 서귀포시 동홍남로 73 1층 미네일</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/littlefella_lf</t>
+          <t>https://www.instagram.com/minail7324199</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -30707,30 +30699,8212 @@
         </is>
       </c>
       <c r="P329" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>1</v>
+      </c>
+      <c r="R329" t="n">
+        <v>32</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>37852718</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37852718</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>동백살롱</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>dongbaek_salong@naver.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>0507-1469-0254</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 연삼로 56 2층 동백살롱</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dongbaek_salong_nail/</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>365</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>52</v>
+      </c>
+      <c r="R330" t="n">
+        <v>417</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>37171482</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37171482</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>라뽐므</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>0703___@naver.com</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 고산동산2길 5 2층</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lapomme_nail_jeju</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>10</v>
+      </c>
+      <c r="R331" t="n">
+        <v>167</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>1917040520</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1917040520</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>단미네일</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>064-753-0274</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 태성로2길 40</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>1</v>
+      </c>
+      <c r="R332" t="n">
+        <v>23</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>1618859421</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1618859421</t>
+        </is>
+      </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>휘연네일</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr"/>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>0507-1370-3935</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 아란9길 23 1층</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sWpkly0h</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P333" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>1</v>
+      </c>
+      <c r="R333" t="n">
+        <v>22</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>2037925870</t>
+        </is>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2037925870</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>바름네일</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>064-744-4142</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 월랑로8길 1 1층 105호</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/barum.nail_jeju</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P334" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>1</v>
+      </c>
+      <c r="R334" t="n">
+        <v>29</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T334" t="inlineStr">
+        <is>
+          <t>305605037</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/305605037</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>네일마커</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr"/>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>064-783-1012</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 성산읍 고성동서로56번길 10-1 1층</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_marker</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P335" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>0</v>
+      </c>
+      <c r="R335" t="n">
+        <v>4</v>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T335" t="inlineStr">
+        <is>
+          <t>1348294347</t>
+        </is>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1348294347</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>네일금비</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>0507-1456-0184</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 솔동산로22번길 18-4 1층</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_ppxlxaG</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P336" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>0</v>
+      </c>
+      <c r="R336" t="n">
+        <v>83</v>
+      </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T336" t="inlineStr">
+        <is>
+          <t>1421848631</t>
+        </is>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1421848631</t>
+        </is>
+      </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>네일또와</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>sj330035@naver.com</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>0507-1387-9214</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 연동4길 36 뜨레모아1층 네일또와</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P337" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>1</v>
+      </c>
+      <c r="R337" t="n">
+        <v>2</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T337" t="inlineStr">
+        <is>
+          <t>1008345244</t>
+        </is>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1008345244</t>
+        </is>
+      </c>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>빈네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>whoabc@naver.com</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>0507-1311-7131</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 표선면 번영로3428번길 129 상가동 102호(gs편의점 옆)</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bin_nail.studio</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P338" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>9</v>
+      </c>
+      <c r="R338" t="n">
+        <v>116</v>
+      </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T338" t="inlineStr">
+        <is>
+          <t>1148723821</t>
+        </is>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1148723821</t>
+        </is>
+      </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>네일더끌림</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>rlduswlsl84@naver.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>0507-1374-0558</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 천지로 20 2층</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>http://instagram.com/___.cclim</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P339" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>6</v>
+      </c>
+      <c r="R339" t="n">
+        <v>14</v>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T339" t="inlineStr">
+        <is>
+          <t>1315971497</t>
+        </is>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1315971497</t>
+        </is>
+      </c>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>제이유네일</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>ehl98@naver.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>0507-1371-5136</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 진군남2길 3 1층 제이유네일</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/junail._?igsh=MTE0aDQ3dG1jb3hwYw%3D%3D</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P340" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>18</v>
+      </c>
+      <c r="R340" t="n">
+        <v>81</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T340" t="inlineStr">
+        <is>
+          <t>1187353619</t>
+        </is>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1187353619</t>
+        </is>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>오드리샵</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>skinbeauty7@naver.com</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>0507-1398-7325</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 성산읍 산성효자로 11-7 퍼스트빌C 1층오드리샵</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/audreyshop_00</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P341" t="n">
+        <v>62</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>0</v>
+      </c>
+      <c r="R341" t="n">
+        <v>62</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>1685197213</t>
+        </is>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1685197213</t>
+        </is>
+      </c>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>요이네일</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>0507-1312-9744</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 신서귀로 43 203호</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yoi.nail_</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P342" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>1</v>
+      </c>
+      <c r="R342" t="n">
+        <v>15</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T342" t="inlineStr">
+        <is>
+          <t>2071583094</t>
+        </is>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2071583094</t>
+        </is>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>닥터아이티엔 강남스킨케어</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>0507-1398-8829</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 태평로431번길 3 디아일랜드블루호텔1층 102호</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kangnambeauty_jeju</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P343" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>83</v>
+      </c>
+      <c r="R343" t="n">
+        <v>186</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T343" t="inlineStr">
+        <is>
+          <t>21018516</t>
+        </is>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21018516</t>
+        </is>
+      </c>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>에마블네일</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr"/>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>0507-1364-2871</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 노연로 139 1층</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aimablenail_jeju</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P344" t="n">
+        <v>117</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>3</v>
+      </c>
+      <c r="R344" t="n">
+        <v>120</v>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T344" t="inlineStr">
+        <is>
+          <t>1244404640</t>
+        </is>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1244404640</t>
+        </is>
+      </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>요아소비제주뷰티</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>0507-1397-8601</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 서광로 288 1층 106호</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yoasobi_jeju</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P345" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>0</v>
+      </c>
+      <c r="R345" t="n">
+        <v>13</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T345" t="inlineStr">
+        <is>
+          <t>1863906024</t>
+        </is>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1863906024</t>
+        </is>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>소미네일</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>0507-1472-2591</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 다랑곶6길 58 다모아빌라 1층</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P346" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>0</v>
+      </c>
+      <c r="R346" t="n">
+        <v>4</v>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>1241214324</t>
+        </is>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1241214324</t>
+        </is>
+      </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>일로네일</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>wjdwldms0706@naver.com</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>0507-1387-7458</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 용담로 126 1층</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/___illonail</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P347" t="n">
+        <v>205</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>4</v>
+      </c>
+      <c r="R347" t="n">
+        <v>209</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>1707032760</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1707032760</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>버디네일</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>hhj6910@naver.com</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 법환상로 20 F동 102호</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__buddy.nail</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P348" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>4</v>
+      </c>
+      <c r="R348" t="n">
+        <v>174</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>1805642729</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1805642729</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>네일스케치</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>nailsketch@naver.com</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>0507-1301-7620</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 오복2길 31-14 2층</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nailsketch</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P349" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>0</v>
+      </c>
+      <c r="R349" t="n">
+        <v>3</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T349" t="inlineStr">
+        <is>
+          <t>13418261</t>
+        </is>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13418261</t>
+        </is>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>동동네일</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>0507-1341-7009</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 신성로 83 1층</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P350" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>0</v>
+      </c>
+      <c r="R350" t="n">
+        <v>0</v>
+      </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T350" t="inlineStr">
+        <is>
+          <t>1163350769</t>
+        </is>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1163350769</t>
+        </is>
+      </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>바른네일</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>fforever1130@naver.com</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>0507-1485-1277</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 신동로67번길 13 B동 101호</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bareun_nail_</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P351" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>0</v>
+      </c>
+      <c r="R351" t="n">
+        <v>17</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T351" t="inlineStr">
+        <is>
+          <t>1511574554</t>
+        </is>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1511574554</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Jeju88nail</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>0507-1403-8866</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 달마루길 20-3 1층</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jeju88nail</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P352" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>20</v>
+      </c>
+      <c r="R352" t="n">
+        <v>21</v>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>1084563175</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1084563175</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>미니네일</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>0507-1335-4182</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 서광로 288 1층 103호</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P353" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>36</v>
+      </c>
+      <c r="R353" t="n">
+        <v>124</v>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>1587118798</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1587118798</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>스테파니네일</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 월광로 140 1층 104호 스테파니네일&amp;온열테라피</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P354" t="n">
+        <v>197</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>9</v>
+      </c>
+      <c r="R354" t="n">
+        <v>206</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>1699828933</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1699828933</t>
+        </is>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>네일히얼Nail Here 여기네일샵</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>yeogiya_beauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>0507-1491-2139</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 노형11길 5-5 미르빌딩 4층 404호</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_herehere</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P355" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>1</v>
+      </c>
+      <c r="R355" t="n">
+        <v>6</v>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>1150525320</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1150525320</t>
+        </is>
+      </c>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>토비네일</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>0507-1397-1082</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 월랑로2길 30 1층</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_mYjxiG</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P356" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>1</v>
+      </c>
+      <c r="R356" t="n">
+        <v>11</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>1957359052</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1957359052</t>
+        </is>
+      </c>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>레푸스노형점</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>refussjeju@naver.com</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>0507-1433-1973</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 연북로 1 롯데마트 4층</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>https://refussjeju.com</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P357" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>240</v>
+      </c>
+      <c r="R357" t="n">
+        <v>310</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>31229697</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31229697</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>이트네일</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>kjw9909ing@naver.com</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>0507-1472-5962</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 안덕면 산방로 3 1층 이트네일 스튜디오</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yeet_nail</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P358" t="n">
+        <v>124</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>6</v>
+      </c>
+      <c r="R358" t="n">
+        <v>130</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>1772939138</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1772939138</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>네일링</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>gulgomi@naver.com</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>0507-1361-1497</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 달마루길 10-3 1층</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_ring_/?igshid=NTc4MTIwNjQ2YQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P359" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>0</v>
+      </c>
+      <c r="R359" t="n">
+        <v>1</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>1213432043</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1213432043</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>린네일 제주노형점</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>0507-1397-8687</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 진군2길 15-9 1층 린네일</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P360" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>0</v>
+      </c>
+      <c r="R360" t="n">
+        <v>500</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>1272276511</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1272276511</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>네일또만나</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>ehgptn321@naver.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 동홍남로 81 1층 네일또만나</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail.ddomanna</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P361" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>0</v>
+      </c>
+      <c r="R361" t="n">
+        <v>80</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>1951868768</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1951868768</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>마루네일</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>0507-1319-0965</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 조천읍 함덕5길 14 1층 천마에버하임 103호</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://toss-order.tossplace.com/booking/QHGa3f5GOp2nGYB</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P362" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>2</v>
+      </c>
+      <c r="R362" t="n">
+        <v>11</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>1803002677</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1803002677</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>h1258</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>jeju_1258@naver.com</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>064-900-1258</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 동광로3길 3 장원스카이팰리스 1층 뒷편상가</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jeju_1258</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P363" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>0</v>
+      </c>
+      <c r="R363" t="n">
+        <v>0</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>1096637563</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1096637563</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>네일보니타</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>064-711-8558</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 연동4길 36</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P364" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>0</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>691164385</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/691164385</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>민아뷰티샵</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>sanso267@naver.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 표선면 표선중앙로 93 1층</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P365" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>0</v>
+      </c>
+      <c r="R365" t="n">
+        <v>0</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>1779957700</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1779957700</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>비비네일</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>milkycoco95@naver.com</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>064-732-0365</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 중정로 45</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P366" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q366" t="n">
+        <v>1</v>
+      </c>
+      <c r="R366" t="n">
+        <v>6</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>30855716</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/30855716</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>네일욜로</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>s2s20228@naver.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>064-711-4155</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 수덕3길 6-1</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/me/nailYOLO</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P367" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q367" t="n">
+        <v>0</v>
+      </c>
+      <c r="R367" t="n">
+        <v>22</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>37991371</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37991371</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>리본뷰티</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>rebornbeauty_jeju@naver.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>0507-1332-0795</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 청사로 67</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rebornbeauty_jeju</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P368" t="n">
+        <v>559</v>
+      </c>
+      <c r="Q368" t="n">
+        <v>101</v>
+      </c>
+      <c r="R368" t="n">
+        <v>660</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>1523223228</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1523223228</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>블랙바비네일</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>blackbarbienail@naver.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 노형2길 1 1층 101호</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/blackbarbienail</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P369" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q369" t="n">
+        <v>5</v>
+      </c>
+      <c r="R369" t="n">
+        <v>9</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>1558308422</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1558308422</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>네일더설렘</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>eyefatoat@naver.com</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>0507-1419-2372</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 애월읍 하귀동남1길 32-14 1층</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailthesulrem0121</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P370" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q370" t="n">
+        <v>43</v>
+      </c>
+      <c r="R370" t="n">
+        <v>133</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>1787765214</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1787765214</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>네일팔레트</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>nail4season@naver.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>0507-1316-6385</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 대정읍 보성구억로 209</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P371" t="n">
+        <v>86</v>
+      </c>
+      <c r="Q371" t="n">
+        <v>0</v>
+      </c>
+      <c r="R371" t="n">
+        <v>86</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>1096198009</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1096198009</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>쏭네일</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>lgy0855@naver.com</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>0507-1489-8579</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 병풍길 20-5 1층(도남) 전 구신중</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P372" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q372" t="n">
+        <v>0</v>
+      </c>
+      <c r="R372" t="n">
+        <v>0</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>1276083345</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1276083345</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>네일마커</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>reform6752@naver.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 성산읍 고성동서로56번길 10-1</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_marker</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P373" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q373" t="n">
+        <v>0</v>
+      </c>
+      <c r="R373" t="n">
+        <v>3</v>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>1224022839</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1224022839</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>르브아네일</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>sunre34@naver.com</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>0507-1331-7347</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 독짓골4길 14 1층 르브아네일</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s29ngUge</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P374" t="n">
+        <v>271</v>
+      </c>
+      <c r="Q374" t="n">
+        <v>3</v>
+      </c>
+      <c r="R374" t="n">
+        <v>274</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>1430025817</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1430025817</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>네일몽슈슈</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>sweet_hae@naver.com</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 오라로 2</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_monchou22</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P375" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q375" t="n">
+        <v>0</v>
+      </c>
+      <c r="R375" t="n">
+        <v>6</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>1299417459</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1299417459</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>향블리네일</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>tonyhm1126@naver.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>070-4548-2911</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 연수로 3 1층 향블리네일</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_hyangvely</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P376" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q376" t="n">
+        <v>2</v>
+      </c>
+      <c r="R376" t="n">
+        <v>92</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>1462323758</t>
+        </is>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1462323758</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>제이네일뷰티</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>064-758-0328</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 정든로 36 1층</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P377" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q377" t="n">
+        <v>1</v>
+      </c>
+      <c r="R377" t="n">
+        <v>3</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>2083401642</t>
+        </is>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2083401642</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>살롱드민</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>top1234mj@naver.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>0507-1315-0490</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 연화로1길 30 살롱드민</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/top1234mj</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P378" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q378" t="n">
+        <v>153</v>
+      </c>
+      <c r="R378" t="n">
+        <v>219</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>1675740938</t>
+        </is>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1675740938</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>오리엔스</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>inter_tarot@naver.com</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 남원읍 태위로 72</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P379" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q379" t="n">
+        <v>0</v>
+      </c>
+      <c r="R379" t="n">
+        <v>3</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>1771280157</t>
+        </is>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1771280157</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>네일 캄 아틀리에</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>choeundham@naver.com</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>0507-1308-0694</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 광양10길 16 2층</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailcalm2</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P380" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q380" t="n">
+        <v>0</v>
+      </c>
+      <c r="R380" t="n">
+        <v>0</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>2067104046</t>
+        </is>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067104046</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>네일현</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>dlwlgp031@naver.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>0507-1335-4877</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 노형로 363 2</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P381" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q381" t="n">
+        <v>0</v>
+      </c>
+      <c r="R381" t="n">
+        <v>0</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>1434661007</t>
+        </is>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1434661007</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>네일소라</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>0507-1325-1790</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 노형12길 24 상가동 101호</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_sora_</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P382" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>0</v>
+      </c>
+      <c r="R382" t="n">
+        <v>8</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>1883410246</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1883410246</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>아델린뷰티</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>nardyzone@naver.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>0507-1391-7971</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 고산동산2길 5 2층 아델린뷰티</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/adeline_beauty__?igsh=OGN3NzlqZGFnOGpy</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P383" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>31</v>
+      </c>
+      <c r="R383" t="n">
+        <v>125</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>1215373649</t>
+        </is>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1215373649</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>니브네일</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>suzzie-@naver.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>0507-1339-4446</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 노형5길 28 삼우빌 1층</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_IkLPb</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P384" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>3</v>
+      </c>
+      <c r="R384" t="n">
+        <v>10</v>
+      </c>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>1757306420</t>
+        </is>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1757306420</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>소랑길뷰티</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>jeanjjangg@naver.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>0507-1422-5324</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 평전길 26 2층 201호</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/soranggil</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P385" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>1</v>
+      </c>
+      <c r="R385" t="n">
+        <v>73</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>1317659508</t>
+        </is>
+      </c>
+      <c r="U385" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1317659508</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>비유네일</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>0507-1433-5234</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 수덕5길 13 머리짱 헤어샵 내부</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/be.u_nail/</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P386" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q386" t="n">
+        <v>1</v>
+      </c>
+      <c r="R386" t="n">
+        <v>9</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>1443830013</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1443830013</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>망고네일</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 연동4길 16-10</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P387" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q387" t="n">
+        <v>0</v>
+      </c>
+      <c r="R387" t="n">
+        <v>8</v>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>1214587619</t>
+        </is>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1214587619</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>네일이 보영</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>kb2329@naver.com</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>0507-1336-5408</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 신대로16길 15 1층 네일이 보영</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail2_bo0</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P388" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q388" t="n">
+        <v>60</v>
+      </c>
+      <c r="R388" t="n">
+        <v>120</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>1173428682</t>
+        </is>
+      </c>
+      <c r="U388" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1173428682</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>류네일</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>0507-1352-7758</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 조천읍 조함해안로 428-18 1층</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P389" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q389" t="n">
+        <v>11</v>
+      </c>
+      <c r="R389" t="n">
+        <v>26</v>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T389" t="inlineStr">
+        <is>
+          <t>1580501252</t>
+        </is>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1580501252</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>소중</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>jmst0704@naver.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>064-792-7782</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 대정읍 글로벌에듀로 390 남영에듀클래스 1층 113호</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/sojungnail</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P390" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>3</v>
+      </c>
+      <c r="R390" t="n">
+        <v>9</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>1896724521</t>
+        </is>
+      </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1896724521</t>
+        </is>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>더블유</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 전농로1길 4</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P391" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q391" t="n">
+        <v>0</v>
+      </c>
+      <c r="R391" t="n">
+        <v>2</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>1120530683</t>
+        </is>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1120530683</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>라벨라네일</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>qhtmf85@naver.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>0507-1407-9416</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 구남동5길 22-1 1층</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P392" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q392" t="n">
+        <v>0</v>
+      </c>
+      <c r="R392" t="n">
+        <v>0</v>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>1878864843</t>
+        </is>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1878864843</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>이디네일</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>phjtogo@naver.com</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 구좌읍 구좌로 91 1층 이디네일</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/e.di_nail</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P393" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>3</v>
+      </c>
+      <c r="R393" t="n">
+        <v>55</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>1079834914</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1079834914</t>
+        </is>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>리파인드네일</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>puherher79@naver.com</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>0507-1432-0519</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 동광로 102 2층 리파인드네일</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/C-6rSu9yz2E/?igsh=MTNtaGdvMG9pMG1vNA==</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P394" t="n">
+        <v>601</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>143</v>
+      </c>
+      <c r="R394" t="n">
+        <v>744</v>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>1925297129</t>
+        </is>
+      </c>
+      <c r="U394" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1925297129</t>
+        </is>
+      </c>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>153네일_파고드는발톱.무좀발톱.물어뜯는손톱.발각질</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>fc5416@naver.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 천제연로 212-1 1층 153네일</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fc5416</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P395" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>18</v>
+      </c>
+      <c r="R395" t="n">
+        <v>58</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>1260273258</t>
+        </is>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1260273258</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>뮤네일</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>mieux_by_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>0507-1376-3652</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 아란7길 8 2층</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jejunail_meu</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P396" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>31</v>
+      </c>
+      <c r="R396" t="n">
+        <v>121</v>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T396" t="inlineStr">
+        <is>
+          <t>1328230165</t>
+        </is>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1328230165</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>살롱멜로</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>jjubika1@naver.com</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>0507-1470-0778</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 신북로 27 1층</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>http://instagram.com/melo_nail_sui</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P397" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>37</v>
+      </c>
+      <c r="R397" t="n">
+        <v>95</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>1190639964</t>
+        </is>
+      </c>
+      <c r="U397" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1190639964</t>
+        </is>
+      </c>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>러브유</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>luvyu_@naver.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>0507-1327-9213</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 신광로 16</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P398" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>0</v>
+      </c>
+      <c r="R398" t="n">
+        <v>1</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T398" t="inlineStr">
+        <is>
+          <t>1937354134</t>
+        </is>
+      </c>
+      <c r="U398" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1937354134</t>
+        </is>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>네일러브다이브</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>lplilelclkl@naver.com</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>0507-1323-3043</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 홍중로27번길 1 1층</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.lovedive</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P399" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>0</v>
+      </c>
+      <c r="R399" t="n">
+        <v>36</v>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>2039322421</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2039322421</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>조이뷰티</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>0507-1336-5423</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 서광로 289 1층</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>http://instagram.com/_joy_beauty_</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P400" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>12</v>
+      </c>
+      <c r="R400" t="n">
+        <v>54</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>1997113427</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1997113427</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>수사랑네일</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>tjgusdl7751@naver.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>0507-1375-3221</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 우정로11길 18 외도부영1차아파트 상가동3층304호</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/soolove_nail</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P401" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>0</v>
+      </c>
+      <c r="R401" t="n">
+        <v>2</v>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>1149959872</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1149959872</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>네일비너스</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>princessphr@naver.com</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 정원로 53 뱀부하우스 1층</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P402" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>0</v>
+      </c>
+      <c r="R402" t="n">
+        <v>0</v>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>1089161914</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1089161914</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>유자살롱</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 진군길 19-2 1층 102호</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P403" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>0</v>
+      </c>
+      <c r="R403" t="n">
+        <v>0</v>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>2064839955</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064839955</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>에스네일</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>snail4324@naver.com</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>064-758-5074</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 설촌로6길 17 1층(삼양이동) RCB</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kangsor_a</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P404" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>4</v>
+      </c>
+      <c r="R404" t="n">
+        <v>7</v>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>1117885685</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1117885685</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>여우놀이터</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>jihye1980@naver.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>064-732-5395</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 동문로 28-1</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P405" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>0</v>
+      </c>
+      <c r="R405" t="n">
+        <v>12</v>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>1481422225</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1481422225</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>네일도</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>jisoo851208@naver.com</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>0507-1495-0512</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 신성로 15 1층</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_nail_do</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P406" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>2</v>
+      </c>
+      <c r="R406" t="n">
+        <v>40</v>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>2078198678</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2078198678</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>네일혜</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>bluei62@naver.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>0507-1359-0854</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 연북로 541 1층 엠헤어스타일 내 (네일혜)</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/__nailhye__</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P407" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>2</v>
+      </c>
+      <c r="R407" t="n">
+        <v>24</v>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>1794401431</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1794401431</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>네일상자</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>jeongej321@naver.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 남성로26길 20 2층(삼도이동)</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/m_nail_box</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P408" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>0</v>
+      </c>
+      <c r="R408" t="n">
+        <v>4</v>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>1001085114</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1001085114</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>아보하네일</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>0507-1368-2460</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 한림읍 한림중앙로 22 1층</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/avoha_nail</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P409" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>0</v>
+      </c>
+      <c r="R409" t="n">
+        <v>70</v>
+      </c>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T409" t="inlineStr">
+        <is>
+          <t>1724265359</t>
+        </is>
+      </c>
+      <c r="U409" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1724265359</t>
+        </is>
+      </c>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>진네일</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>jinnail_@naver.com</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>0507-1375-6020</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 신대로14길 34 2층</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jinnail_</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P410" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>152</v>
+      </c>
+      <c r="R410" t="n">
+        <v>347</v>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T410" t="inlineStr">
+        <is>
+          <t>1687250401</t>
+        </is>
+      </c>
+      <c r="U410" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1687250401</t>
+        </is>
+      </c>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>네일만기다려</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>kiyu13@naver.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>0507-1398-9130</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 고마로 71 2층 201호</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail_gidaryeo</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P411" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>0</v>
+      </c>
+      <c r="R411" t="n">
+        <v>47</v>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T411" t="inlineStr">
+        <is>
+          <t>1407946510</t>
+        </is>
+      </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1407946510</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>은네일</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>eunjihello@naver.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 남녕로 28-1 1층</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eunn3233</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P412" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>45</v>
+      </c>
+      <c r="R412" t="n">
+        <v>116</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T412" t="inlineStr">
+        <is>
+          <t>1929206975</t>
+        </is>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1929206975</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>소네네일</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>ljh6971@naver.com</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>0507-1391-6260</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 신동로27번길 17 1층 소네네일(SONE NAIL)</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sonenail_23</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P413" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>2</v>
+      </c>
+      <c r="R413" t="n">
+        <v>170</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T413" t="inlineStr">
+        <is>
+          <t>1154302277</t>
+        </is>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1154302277</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>달콤살롱</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>830mijung@naver.com</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 정존9길 19 1층 달콤살롱</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mippeum.nail?igsh=MXFsc21nb2x2Y3g0dA==</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P414" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>5</v>
+      </c>
+      <c r="R414" t="n">
+        <v>28</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T414" t="inlineStr">
+        <is>
+          <t>1728912841</t>
+        </is>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1728912841</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>문뷰티샵</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>0507-1326-1951</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 신대로21길 25-3 1층</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P415" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>1</v>
+      </c>
+      <c r="R415" t="n">
+        <v>10</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T415" t="inlineStr">
+        <is>
+          <t>1320740499</t>
+        </is>
+      </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1320740499</t>
+        </is>
+      </c>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>엘리제토탈뷰티</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>giobeauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>064-792-6456</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 대정읍 하모중앙로 63-1</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P416" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>0</v>
+      </c>
+      <c r="R416" t="n">
+        <v>0</v>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T416" t="inlineStr">
+        <is>
+          <t>1541813488</t>
+        </is>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1541813488</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>디자인 수지</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>design-suji@naver.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>0507-1309-2058</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>제주특별자치도 제주시 노형로 21 2층</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/design-suji</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P417" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>0</v>
+      </c>
+      <c r="R417" t="n">
+        <v>0</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T417" t="inlineStr">
+        <is>
+          <t>1189515208</t>
+        </is>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1189515208</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>카페,디저트</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>엘에프</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>woojoo90@naver.com</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>0507-1497-0767</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>제주특별자치도 서귀포시 이어도로 301 4호 엘에프 LF</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/littlefella_lf</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P418" t="n">
         <v>50</v>
       </c>
-      <c r="Q329" t="n">
+      <c r="Q418" t="n">
         <v>2</v>
       </c>
-      <c r="R329" t="n">
+      <c r="R418" t="n">
         <v>52</v>
       </c>
-      <c r="S329" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T329" t="inlineStr">
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T418" t="inlineStr">
         <is>
           <t>2051185030</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="U418" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2051185030</t>
         </is>
       </c>
-      <c r="V329" t="inlineStr">
+      <c r="V418" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
